--- a/pruebas/zamora_TVpromediostotal.xlsx
+++ b/pruebas/zamora_TVpromediostotal.xlsx
@@ -784,29 +784,45 @@
       <c r="B9" s="7" t="n">
         <v>55.25</v>
       </c>
-      <c r="C9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>0</v>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K9" s="7" t="n">
         <v>57.55</v>
@@ -820,8 +836,10 @@
       <c r="N9" s="7" t="n">
         <v>57.49</v>
       </c>
-      <c r="O9" s="7" t="n">
-        <v>0</v>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P9" s="7" t="n">
         <v>56.76</v>
@@ -838,14 +856,20 @@
       <c r="T9" s="7" t="n">
         <v>55.88</v>
       </c>
-      <c r="U9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="7" t="n">
-        <v>0</v>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="X9" s="7" t="n">
         <v>55.13</v>
@@ -853,8 +877,10 @@
       <c r="Y9" s="7" t="n">
         <v>54.41</v>
       </c>
-      <c r="Z9" s="7" t="n">
-        <v>0</v>
+      <c r="Z9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AA9" s="7" t="n">
         <v>55</v>
@@ -865,8 +891,10 @@
       <c r="AC9" s="7" t="n">
         <v>54.2</v>
       </c>
-      <c r="AD9" s="7" t="n">
-        <v>0</v>
+      <c r="AD9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AE9" s="7" t="n">
         <v>54.14</v>
@@ -892,29 +920,45 @@
       <c r="B10" s="7" t="n">
         <v>67.25</v>
       </c>
-      <c r="C10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="7" t="n">
-        <v>0</v>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K10" s="7" t="n">
         <v>38.7</v>
@@ -928,8 +972,10 @@
       <c r="N10" s="7" t="n">
         <v>38.39</v>
       </c>
-      <c r="O10" s="7" t="n">
-        <v>0</v>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P10" s="7" t="n">
         <v>39.4</v>
@@ -946,14 +992,20 @@
       <c r="T10" s="7" t="n">
         <v>38.94</v>
       </c>
-      <c r="U10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="7" t="n">
-        <v>0</v>
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="X10" s="7" t="n">
         <v>39.57</v>
@@ -961,8 +1013,10 @@
       <c r="Y10" s="7" t="n">
         <v>38.75</v>
       </c>
-      <c r="Z10" s="7" t="n">
-        <v>0</v>
+      <c r="Z10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AA10" s="7" t="n">
         <v>39.83</v>
@@ -973,8 +1027,10 @@
       <c r="AC10" s="7" t="n">
         <v>38.66</v>
       </c>
-      <c r="AD10" s="7" t="n">
-        <v>0</v>
+      <c r="AD10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AE10" s="7" t="n">
         <v>40.58</v>
@@ -1000,29 +1056,45 @@
       <c r="B11" s="7" t="n">
         <v>77.25</v>
       </c>
-      <c r="C11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>0</v>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K11" s="7" t="n">
         <v>42.34</v>
@@ -1036,8 +1108,10 @@
       <c r="N11" s="7" t="n">
         <v>39.71</v>
       </c>
-      <c r="O11" s="7" t="n">
-        <v>0</v>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P11" s="7" t="n">
         <v>42.02</v>
@@ -1054,14 +1128,20 @@
       <c r="T11" s="7" t="n">
         <v>42.59</v>
       </c>
-      <c r="U11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="7" t="n">
-        <v>0</v>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="X11" s="7" t="n">
         <v>40.06</v>
@@ -1069,8 +1149,10 @@
       <c r="Y11" s="7" t="n">
         <v>37.89</v>
       </c>
-      <c r="Z11" s="7" t="n">
-        <v>0</v>
+      <c r="Z11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AA11" s="7" t="n">
         <v>41.15</v>
@@ -1081,8 +1163,10 @@
       <c r="AC11" s="7" t="n">
         <v>39.38</v>
       </c>
-      <c r="AD11" s="7" t="n">
-        <v>0</v>
+      <c r="AD11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AE11" s="7" t="n">
         <v>40.89</v>
@@ -1108,29 +1192,45 @@
       <c r="B12" s="7" t="n">
         <v>175.25</v>
       </c>
-      <c r="C12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>0</v>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K12" s="7" t="n">
         <v>32.85</v>
@@ -1144,8 +1244,10 @@
       <c r="N12" s="7" t="n">
         <v>32.62</v>
       </c>
-      <c r="O12" s="7" t="n">
-        <v>0</v>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P12" s="7" t="n">
         <v>35.57</v>
@@ -1162,14 +1264,20 @@
       <c r="T12" s="7" t="n">
         <v>33.94</v>
       </c>
-      <c r="U12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="7" t="n">
-        <v>0</v>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="X12" s="7" t="n">
         <v>33.7</v>
@@ -1177,8 +1285,10 @@
       <c r="Y12" s="7" t="n">
         <v>32.97</v>
       </c>
-      <c r="Z12" s="7" t="n">
-        <v>0</v>
+      <c r="Z12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AA12" s="7" t="n">
         <v>33.07</v>
@@ -1189,8 +1299,10 @@
       <c r="AC12" s="7" t="n">
         <v>33.04</v>
       </c>
-      <c r="AD12" s="7" t="n">
-        <v>0</v>
+      <c r="AD12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AE12" s="7" t="n">
         <v>33.12</v>
@@ -1216,29 +1328,45 @@
       <c r="B13" s="7" t="n">
         <v>187.25</v>
       </c>
-      <c r="C13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>0</v>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K13" s="7" t="n">
         <v>31.68</v>
@@ -1252,8 +1380,10 @@
       <c r="N13" s="7" t="n">
         <v>31.96</v>
       </c>
-      <c r="O13" s="7" t="n">
-        <v>0</v>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P13" s="7" t="n">
         <v>32.38</v>
@@ -1270,14 +1400,20 @@
       <c r="T13" s="7" t="n">
         <v>31.71</v>
       </c>
-      <c r="U13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="7" t="n">
-        <v>0</v>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="X13" s="7" t="n">
         <v>32.34</v>
@@ -1285,8 +1421,10 @@
       <c r="Y13" s="7" t="n">
         <v>32.37</v>
       </c>
-      <c r="Z13" s="7" t="n">
-        <v>0</v>
+      <c r="Z13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AA13" s="7" t="n">
         <v>32.65</v>
@@ -1297,8 +1435,10 @@
       <c r="AC13" s="7" t="n">
         <v>31.78</v>
       </c>
-      <c r="AD13" s="7" t="n">
-        <v>0</v>
+      <c r="AD13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AE13" s="7" t="n">
         <v>31.59</v>
@@ -1324,29 +1464,45 @@
       <c r="B14" s="7" t="n">
         <v>199.25</v>
       </c>
-      <c r="C14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>0</v>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K14" s="7" t="n">
         <v>30.38</v>
@@ -1360,8 +1516,10 @@
       <c r="N14" s="7" t="n">
         <v>30.17</v>
       </c>
-      <c r="O14" s="7" t="n">
-        <v>0</v>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P14" s="7" t="n">
         <v>32.04</v>
@@ -1378,14 +1536,20 @@
       <c r="T14" s="7" t="n">
         <v>30.94</v>
       </c>
-      <c r="U14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="7" t="n">
-        <v>0</v>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="X14" s="7" t="n">
         <v>31.18</v>
@@ -1393,8 +1557,10 @@
       <c r="Y14" s="7" t="n">
         <v>30.95</v>
       </c>
-      <c r="Z14" s="7" t="n">
-        <v>0</v>
+      <c r="Z14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AA14" s="7" t="n">
         <v>30.83</v>
@@ -1405,8 +1571,10 @@
       <c r="AC14" s="7" t="n">
         <v>30.71</v>
       </c>
-      <c r="AD14" s="7" t="n">
-        <v>0</v>
+      <c r="AD14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AE14" s="7" t="n">
         <v>30.44</v>
@@ -1432,29 +1600,45 @@
       <c r="B15" s="7" t="n">
         <v>211.25</v>
       </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>0</v>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K15" s="7" t="n">
         <v>29.23</v>
@@ -1468,8 +1652,10 @@
       <c r="N15" s="7" t="n">
         <v>28.44</v>
       </c>
-      <c r="O15" s="7" t="n">
-        <v>0</v>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P15" s="7" t="n">
         <v>29.66</v>
@@ -1486,14 +1672,20 @@
       <c r="T15" s="7" t="n">
         <v>29.25</v>
       </c>
-      <c r="U15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="7" t="n">
-        <v>0</v>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="X15" s="7" t="n">
         <v>29.75</v>
@@ -1501,8 +1693,10 @@
       <c r="Y15" s="7" t="n">
         <v>29.47</v>
       </c>
-      <c r="Z15" s="7" t="n">
-        <v>0</v>
+      <c r="Z15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AA15" s="7" t="n">
         <v>29.05</v>
@@ -1513,8 +1707,10 @@
       <c r="AC15" s="7" t="n">
         <v>28.38</v>
       </c>
-      <c r="AD15" s="7" t="n">
-        <v>0</v>
+      <c r="AD15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AE15" s="7" t="n">
         <v>29.33</v>
@@ -1540,29 +1736,45 @@
       <c r="B16" s="7" t="n">
         <v>525.25</v>
       </c>
-      <c r="C16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="7" t="n">
-        <v>0</v>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K16" s="7" t="n">
         <v>26.49</v>
@@ -1576,8 +1788,10 @@
       <c r="N16" s="7" t="n">
         <v>26.86</v>
       </c>
-      <c r="O16" s="7" t="n">
-        <v>0</v>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P16" s="7" t="n">
         <v>26.77</v>
@@ -1594,14 +1808,20 @@
       <c r="T16" s="7" t="n">
         <v>26.91</v>
       </c>
-      <c r="U16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="7" t="n">
-        <v>0</v>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="X16" s="7" t="n">
         <v>26.82</v>
@@ -1609,8 +1829,10 @@
       <c r="Y16" s="7" t="n">
         <v>26.87</v>
       </c>
-      <c r="Z16" s="7" t="n">
-        <v>0</v>
+      <c r="Z16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AA16" s="7" t="n">
         <v>26.65</v>
@@ -1621,8 +1843,10 @@
       <c r="AC16" s="7" t="n">
         <v>26.56</v>
       </c>
-      <c r="AD16" s="7" t="n">
-        <v>0</v>
+      <c r="AD16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AE16" s="7" t="n">
         <v>26.93</v>
@@ -1648,29 +1872,45 @@
       <c r="B17" s="7" t="n">
         <v>537.25</v>
       </c>
-      <c r="C17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7" t="n">
-        <v>0</v>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K17" s="7" t="n">
         <v>26.63</v>
@@ -1684,8 +1924,10 @@
       <c r="N17" s="7" t="n">
         <v>26.93</v>
       </c>
-      <c r="O17" s="7" t="n">
-        <v>0</v>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P17" s="7" t="n">
         <v>27.04</v>
@@ -1702,14 +1944,20 @@
       <c r="T17" s="7" t="n">
         <v>27.2</v>
       </c>
-      <c r="U17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="7" t="n">
-        <v>0</v>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="X17" s="7" t="n">
         <v>26.92</v>
@@ -1717,8 +1965,10 @@
       <c r="Y17" s="7" t="n">
         <v>27.06</v>
       </c>
-      <c r="Z17" s="7" t="n">
-        <v>0</v>
+      <c r="Z17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AA17" s="7" t="n">
         <v>26.83</v>
@@ -1729,8 +1979,10 @@
       <c r="AC17" s="7" t="n">
         <v>26.68</v>
       </c>
-      <c r="AD17" s="7" t="n">
-        <v>0</v>
+      <c r="AD17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AE17" s="7" t="n">
         <v>27.21</v>
@@ -1756,29 +2008,45 @@
       <c r="B18" s="7" t="n">
         <v>549.25</v>
       </c>
-      <c r="C18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>0</v>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K18" s="7" t="n">
         <v>27.35</v>
@@ -1792,8 +2060,10 @@
       <c r="N18" s="7" t="n">
         <v>27.55</v>
       </c>
-      <c r="O18" s="7" t="n">
-        <v>0</v>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P18" s="7" t="n">
         <v>28.86</v>
@@ -1810,14 +2080,20 @@
       <c r="T18" s="7" t="n">
         <v>28.35</v>
       </c>
-      <c r="U18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="7" t="n">
-        <v>0</v>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="X18" s="7" t="n">
         <v>27.35</v>
@@ -1825,8 +2101,10 @@
       <c r="Y18" s="7" t="n">
         <v>27.39</v>
       </c>
-      <c r="Z18" s="7" t="n">
-        <v>0</v>
+      <c r="Z18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AA18" s="7" t="n">
         <v>27.07</v>
@@ -1837,8 +2115,10 @@
       <c r="AC18" s="7" t="n">
         <v>27.13</v>
       </c>
-      <c r="AD18" s="7" t="n">
-        <v>0</v>
+      <c r="AD18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AE18" s="7" t="n">
         <v>27.25</v>
@@ -1864,29 +2144,45 @@
       <c r="B19" s="10" t="n">
         <v>681.25</v>
       </c>
-      <c r="C19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>0</v>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K19" s="10" t="n">
         <v>27.51</v>
@@ -1900,8 +2196,10 @@
       <c r="N19" s="10" t="n">
         <v>27.63</v>
       </c>
-      <c r="O19" s="10" t="n">
-        <v>0</v>
+      <c r="O19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P19" s="10" t="n">
         <v>27.18</v>
@@ -1918,14 +2216,20 @@
       <c r="T19" s="10" t="n">
         <v>27.61</v>
       </c>
-      <c r="U19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="10" t="n">
-        <v>0</v>
+      <c r="U19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="X19" s="10" t="n">
         <v>27.49</v>
@@ -1933,8 +2237,10 @@
       <c r="Y19" s="10" t="n">
         <v>27.51</v>
       </c>
-      <c r="Z19" s="10" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AA19" s="10" t="n">
         <v>27.53</v>
@@ -1945,8 +2251,10 @@
       <c r="AC19" s="10" t="n">
         <v>27.33</v>
       </c>
-      <c r="AD19" s="10" t="n">
-        <v>0</v>
+      <c r="AD19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AE19" s="10" t="n">
         <v>27.68</v>
